--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>124825300</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>91186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124825300</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91248</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trängslet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>427070</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6805707</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering. Hålträd</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>124825300</v>
       </c>
       <c r="B4" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>124825300</v>
       </c>
       <c r="B4" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>124825300</v>
       </c>
       <c r="B4" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>124825300</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>124825300</v>
       </c>
       <c r="B4" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22191-2025 artfynd.xlsx
+++ b/artfynd/A 22191-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>124825300</v>
       </c>
       <c r="B4" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
